--- a/GT_case/notebooks/notebook_pLCA_wo_dynamic/comp_pGWP100vsGWP100/scope1and3_selected_(bio)diesel.xlsx
+++ b/GT_case/notebooks/notebook_pLCA_wo_dynamic/comp_pGWP100vsGWP100/scope1and3_selected_(bio)diesel.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>diesel, ecoinvent</t>
   </si>
@@ -31,34 +31,61 @@
     <t>scope 1</t>
   </si>
   <si>
-    <t>premise_GWP100</t>
-  </si>
-  <si>
-    <t>pGWP100, SSP1-19, MY2030</t>
-  </si>
-  <si>
-    <t>pGWP100, SSP1-19, MY2040</t>
-  </si>
-  <si>
-    <t>pGWP100, SSP1-19, MY2050</t>
-  </si>
-  <si>
-    <t>pGWP100, SSP2-45, MY2030</t>
-  </si>
-  <si>
-    <t>pGWP100, SSP2-45, MY2040</t>
-  </si>
-  <si>
-    <t>pGWP100, SSP2-45, MY2050</t>
-  </si>
-  <si>
-    <t>pGWP100, SSP5-85, MY2030</t>
-  </si>
-  <si>
-    <t>pGWP100, SSP5-85, MY2040</t>
-  </si>
-  <si>
-    <t>pGWP100, SSP5-85, MY2050</t>
+    <t>premise GWP100</t>
+  </si>
+  <si>
+    <t>pGWP100 dpAGWP[CO2], SSP1-19, MY2030</t>
+  </si>
+  <si>
+    <t>pGWP100 dpAGWP[CO2], SSP1-19, MY2040</t>
+  </si>
+  <si>
+    <t>pGWP100 dpAGWP[CO2], SSP1-19, MY2050</t>
+  </si>
+  <si>
+    <t>pGWP100 dpAGWP[CO2], SSP2-45, MY2030</t>
+  </si>
+  <si>
+    <t>pGWP100 dpAGWP[CO2], SSP2-45, MY2040</t>
+  </si>
+  <si>
+    <t>pGWP100 dpAGWP[CO2], SSP2-45, MY2050</t>
+  </si>
+  <si>
+    <t>pGWP100 dpAGWP[CO2], SSP5-85, MY2030</t>
+  </si>
+  <si>
+    <t>pGWP100 dpAGWP[CO2], SSP5-85, MY2040</t>
+  </si>
+  <si>
+    <t>pGWP100 dpAGWP[CO2], SSP5-85, MY2050</t>
+  </si>
+  <si>
+    <t>pGWP100 fixed AGWP[CO2], SSP1-19, MY2030</t>
+  </si>
+  <si>
+    <t>pGWP100 fixed AGWP[CO2], SSP1-19, MY2040</t>
+  </si>
+  <si>
+    <t>pGWP100 fixed AGWP[CO2], SSP1-19, MY2050</t>
+  </si>
+  <si>
+    <t>pGWP100 fixed AGWP[CO2], SSP2-45, MY2030</t>
+  </si>
+  <si>
+    <t>pGWP100 fixed AGWP[CO2], SSP2-45, MY2040</t>
+  </si>
+  <si>
+    <t>pGWP100 fixed AGWP[CO2], SSP2-45, MY2050</t>
+  </si>
+  <si>
+    <t>pGWP100 fixed AGWP[CO2], SSP5-85, MY2030</t>
+  </si>
+  <si>
+    <t>pGWP100 fixed AGWP[CO2], SSP5-85, MY2040</t>
+  </si>
+  <si>
+    <t>pGWP100 fixed AGWP[CO2], SSP5-85, MY2050</t>
   </si>
 </sst>
 </file>
@@ -416,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -463,7 +490,7 @@
         <v>21.96402308669757</v>
       </c>
       <c r="C4">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D4">
         <v>-60.56654443113783</v>
@@ -486,7 +513,7 @@
         <v>20.52414410732841</v>
       </c>
       <c r="C5">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D5">
         <v>-60.90177872665178</v>
@@ -509,7 +536,7 @@
         <v>20.99584382718717</v>
       </c>
       <c r="C6">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D6">
         <v>-60.79928100627303</v>
@@ -532,7 +559,7 @@
         <v>21.13022248284281</v>
       </c>
       <c r="C7">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D7">
         <v>-60.7714711330169</v>
@@ -555,7 +582,7 @@
         <v>20.24304496664647</v>
       </c>
       <c r="C8">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D8">
         <v>-60.96212752491029</v>
@@ -578,7 +605,7 @@
         <v>20.84493903872912</v>
       </c>
       <c r="C9">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D9">
         <v>-60.82853261145367</v>
@@ -601,7 +628,7 @@
         <v>21.30578083512389</v>
       </c>
       <c r="C10">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D10">
         <v>-60.72609838751386</v>
@@ -624,7 +651,7 @@
         <v>19.82112504518727</v>
       </c>
       <c r="C11">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D11">
         <v>-61.05396895663441</v>
@@ -647,7 +674,7 @@
         <v>19.97223716622905</v>
       </c>
       <c r="C12">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D12">
         <v>-61.01746254064086</v>
@@ -670,7 +697,7 @@
         <v>20.6833183875221</v>
       </c>
       <c r="C13">
-        <v>74.467</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="D13">
         <v>-60.85724016562968</v>
@@ -682,6 +709,213 @@
         <v>-16.49203417928222</v>
       </c>
       <c r="G13">
+        <v>72.16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>23.49838614382448</v>
+      </c>
+      <c r="C14">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="D14">
+        <v>-69.72899284299051</v>
+      </c>
+      <c r="E14">
+        <v>72.16</v>
+      </c>
+      <c r="F14">
+        <v>-22.84631526766357</v>
+      </c>
+      <c r="G14">
+        <v>72.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>23.79613809875594</v>
+      </c>
+      <c r="C15">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="D15">
+        <v>-68.86157083329886</v>
+      </c>
+      <c r="E15">
+        <v>72.16</v>
+      </c>
+      <c r="F15">
+        <v>-22.7961995525188</v>
+      </c>
+      <c r="G15">
+        <v>72.16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>24.06353933619629</v>
+      </c>
+      <c r="C16">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="D16">
+        <v>-69.20399687953672</v>
+      </c>
+      <c r="E16">
+        <v>72.16</v>
+      </c>
+      <c r="F16">
+        <v>-23.54425090710454</v>
+      </c>
+      <c r="G16">
+        <v>72.16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>22.65588848344882</v>
+      </c>
+      <c r="C17">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="D17">
+        <v>-68.21450013787585</v>
+      </c>
+      <c r="E17">
+        <v>72.16</v>
+      </c>
+      <c r="F17">
+        <v>-21.89514552124011</v>
+      </c>
+      <c r="G17">
+        <v>72.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>21.96474055700278</v>
+      </c>
+      <c r="C18">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="D18">
+        <v>-64.04823670772235</v>
+      </c>
+      <c r="E18">
+        <v>72.16</v>
+      </c>
+      <c r="F18">
+        <v>-19.72624473530414</v>
+      </c>
+      <c r="G18">
+        <v>72.16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>21.22322316324142</v>
+      </c>
+      <c r="C19">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="D19">
+        <v>-60.42193401794308</v>
+      </c>
+      <c r="E19">
+        <v>72.16</v>
+      </c>
+      <c r="F19">
+        <v>-17.97314284957729</v>
+      </c>
+      <c r="G19">
+        <v>72.16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>21.82043201547213</v>
+      </c>
+      <c r="C20">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="D20">
+        <v>-67.19158681839005</v>
+      </c>
+      <c r="E20">
+        <v>72.16</v>
+      </c>
+      <c r="F20">
+        <v>-21.43234198847503</v>
+      </c>
+      <c r="G20">
+        <v>72.16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>20.05384480898881</v>
+      </c>
+      <c r="C21">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="D21">
+        <v>-61.21896353763928</v>
+      </c>
+      <c r="E21">
+        <v>72.16</v>
+      </c>
+      <c r="F21">
+        <v>-18.25695604152724</v>
+      </c>
+      <c r="G21">
+        <v>72.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22">
+        <v>18.71003320006263</v>
+      </c>
+      <c r="C22">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="D22">
+        <v>-54.97571850020528</v>
+      </c>
+      <c r="E22">
+        <v>72.16</v>
+      </c>
+      <c r="F22">
+        <v>-14.75103153563409</v>
+      </c>
+      <c r="G22">
         <v>72.16</v>
       </c>
     </row>
